--- a/docs/review/launch-set.xlsx
+++ b/docs/review/launch-set.xlsx
@@ -11403,7 +11403,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>band_lat_pulldown.f.mp4</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>band_overhead_press.f.mp4</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>band_overhead_press.m.mp4</t>
         </is>
       </c>
       <c r="G131" s="8" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>band_pull_apart.f.mp4</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>band_pull_apart.m.mp4</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>bridge_floor_press.f.mp4</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>cable_chest_fly.m.mp4</t>
         </is>
       </c>
       <c r="G137" s="8" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>cable_woodchop.f.mp4</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>missing (coming)</t>
+          <t>cable_woodchop.m.mp4</t>
         </is>
       </c>
       <c r="G139" s="8" t="inlineStr">

--- a/docs/review/launch-set.xlsx
+++ b/docs/review/launch-set.xlsx
@@ -20292,12 +20292,12 @@
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>overhead_dumbbell_triceps_extension</t>
+          <t>dumbbell_kickback</t>
         </is>
       </c>
       <c r="C237" s="8" t="inlineStr">
         <is>
-          <t>Overhead triceps extension</t>
+          <t>Dumbbell triceps kickback</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr">
@@ -20317,12 +20317,13 @@
       </c>
       <c r="G237" s="8" t="inlineStr">
         <is>
-          <t>Triceps (Triceps brachii): primary, 1.0</t>
+          <t>Triceps (Triceps brachii): primary, 1.0
+Rear shoulders (Deltoid · rear head): secondary, 0.2</t>
         </is>
       </c>
       <c r="H237" s="8" t="inlineStr">
         <is>
-          <t>Dumbbells</t>
+          <t>Dumbbells, Flat bench</t>
         </is>
       </c>
       <c r="I237" s="8" t="inlineStr">
@@ -20331,7 +20332,7 @@
         </is>
       </c>
       <c r="J237" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K237" s="8" t="inlineStr">
         <is>
@@ -20340,17 +20341,17 @@
       </c>
       <c r="L237" s="8" t="inlineStr">
         <is>
-          <t>Standing, Seated</t>
+          <t>Standing, With support</t>
         </is>
       </c>
       <c r="M237" s="8" t="inlineStr">
         <is>
-          <t>Shoulder, Elbow / wrist</t>
+          <t>Elbow / wrist, Recent surgery</t>
         </is>
       </c>
       <c r="N237" s="8" t="inlineStr">
         <is>
-          <t>Hold a dumbbell overhead; lower behind your head and extend.</t>
+          <t>One hand on the bench, upper arm along your side, straighten the elbow back and squeeze.</t>
         </is>
       </c>
       <c r="O237" s="8" t="inlineStr">
@@ -20360,10 +20361,9 @@
       </c>
       <c r="P237" s="8" t="inlineStr">
         <is>
-          <t>Shoulder: Arm overhead (full)
-Elbow: Straighten elbow with weight (full)
-Elbow: Bend elbow with weight (full)
-Wrist: Grip tight (full)</t>
+          <t>Elbow: Straighten elbow with weight (full)
+Shoulder: Pull (hold, no movement)
+Wrist: Grip tight (partial)</t>
         </is>
       </c>
       <c r="Q237" s="9" t="n"/>

--- a/docs/review/launch-set.xlsx
+++ b/docs/review/launch-set.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Launch set" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Launch set'!$A$1:$R$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Launch set'!$A$1:$R$245</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>243 exercises go to the first store release. Nothing reaches users until you approve it.</t>
+          <t>244 exercises go to the first store release. Nothing reaches users until you approve it.</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTA('Launch set'!$B$2:$B$244)</f>
+        <f>COUNTA('Launch set'!$B$2:$B$245)</f>
         <v/>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF('Launch set'!$Q$2:$Q$244,"Approve")</f>
+        <f>COUNTIF('Launch set'!$Q$2:$Q$245,"Approve")</f>
         <v/>
       </c>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF('Launch set'!$Q$2:$Q$244,"Adjust")</f>
+        <f>COUNTIF('Launch set'!$Q$2:$Q$245,"Adjust")</f>
         <v/>
       </c>
     </row>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF('Launch set'!$Q$2:$Q$244,"Reject")</f>
+        <f>COUNTIF('Launch set'!$Q$2:$Q$245,"Reject")</f>
         <v/>
       </c>
     </row>
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R244"/>
+  <dimension ref="A1:R245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -20948,10 +20948,91 @@
       <c r="Q244" s="9" t="n"/>
       <c r="R244" s="9" t="n"/>
     </row>
+    <row r="245">
+      <c r="A245" s="8" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>su_seated_shrug_hold</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>Seated shrug with pause</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>Shoulder program</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="inlineStr">
+        <is>
+          <t>missing (coming)</t>
+        </is>
+      </c>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>missing (coming)</t>
+        </is>
+      </c>
+      <c r="G245" s="8" t="inlineStr">
+        <is>
+          <t>Traps (Trapezius): primary, 0.8
+Upper back (Rhomboids and middle trapezius): secondary, 0.3</t>
+        </is>
+      </c>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>Bodyweight</t>
+        </is>
+      </c>
+      <c r="I245" s="8" t="inlineStr">
+        <is>
+          <t>Home, Gym, Outdoors</t>
+        </is>
+      </c>
+      <c r="J245" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" s="8" t="inlineStr">
+        <is>
+          <t>9+ (kids)</t>
+        </is>
+      </c>
+      <c r="L245" s="8" t="inlineStr">
+        <is>
+          <t>Standing, With support, Seated</t>
+        </is>
+      </c>
+      <c r="M245" s="8" t="inlineStr">
+        <is>
+          <t>Neck, Shoulder, Recent surgery</t>
+        </is>
+      </c>
+      <c r="N245" s="8" t="inlineStr">
+        <is>
+          <t>Sit tall, lift both shoulders toward your ears, hold two seconds, then lower slowly.</t>
+        </is>
+      </c>
+      <c r="O245" s="8" t="inlineStr">
+        <is>
+          <t>Main work</t>
+        </is>
+      </c>
+      <c r="P245" s="8" t="inlineStr">
+        <is>
+          <t>Shoulder: Carry weight (partial)</t>
+        </is>
+      </c>
+      <c r="Q245" s="9" t="n"/>
+      <c r="R245" s="9" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R244"/>
+  <autoFilter ref="A1:R245"/>
   <dataValidations count="1">
-    <dataValidation sqref="Q2:Q244" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve, Adjust or Reject." prompt="Approve, or Adjust / Reject and explain in Comment." type="list">
+    <dataValidation sqref="Q2:Q245" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Choose Approve, Adjust or Reject." prompt="Approve, or Adjust / Reject and explain in Comment." type="list">
       <formula1>"Approve,Adjust,Reject"</formula1>
     </dataValidation>
   </dataValidations>
